--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386E5AFA-BB62-4CE5-BB0B-1C621B48EA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35962B79-B830-492F-A8FD-2546973C1C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23580" yWindow="555" windowWidth="19335" windowHeight="20535" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="1050" yWindow="900" windowWidth="19335" windowHeight="16710" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="89">
   <si>
     <t>Cargo</t>
   </si>
@@ -202,16 +202,121 @@
   </si>
   <si>
     <t>Domingo</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 1</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 2</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 3</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 4</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 5</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 6</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 7</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 8</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 9</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 10</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 11</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 12</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 13</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 14</t>
+  </si>
+  <si>
+    <t>Tenico de Ejecucion 15</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 1</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 2</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 3</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 4</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 5</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 6</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 7</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 8</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 9</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 10</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 11</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 12</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 13</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 14</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 15</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución 16</t>
+  </si>
+  <si>
+    <t>Auxiliar de Ejecución de la operación</t>
+  </si>
+  <si>
+    <t>Tecnico Ejecución de la Operación</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -553,10 +658,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1098,7 +1204,349 @@
         <v>55</v>
       </c>
     </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" t="s">
+        <v>87</v>
+      </c>
+      <c r="C72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" t="s">
+        <v>87</v>
+      </c>
+      <c r="C73" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>87</v>
+      </c>
+      <c r="C74" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>87</v>
+      </c>
+      <c r="C75" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35962B79-B830-492F-A8FD-2546973C1C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC92EC8A-299F-420B-BDCE-1BBD5061BD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="900" windowWidth="19335" windowHeight="16710" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="97">
   <si>
     <t>Cargo</t>
   </si>
@@ -301,6 +301,30 @@
   </si>
   <si>
     <t>Tecnico Ejecución de la Operación</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Cablemovil</t>
+  </si>
+  <si>
+    <t>Greenmovil</t>
+  </si>
+  <si>
+    <t>Inspector de Seguridad vial</t>
+  </si>
+  <si>
+    <t>Inspector de Seguridad vial 1</t>
+  </si>
+  <si>
+    <t>Inspector de Seguridad vial 2</t>
+  </si>
+  <si>
+    <t>Inspector de Seguridad vial 3</t>
+  </si>
+  <si>
+    <t>Inspector de Seguridad vial 4</t>
   </si>
 </sst>
 </file>
@@ -658,14 +682,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -675,8 +699,11 @@
       <c r="C1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -686,8 +713,11 @@
       <c r="C2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -697,8 +727,11 @@
       <c r="C3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -708,8 +741,11 @@
       <c r="C4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -719,8 +755,11 @@
       <c r="C5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -730,8 +769,11 @@
       <c r="C6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -741,8 +783,11 @@
       <c r="C7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -752,8 +797,11 @@
       <c r="C8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -763,8 +811,11 @@
       <c r="C9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -774,8 +825,11 @@
       <c r="C10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -785,8 +839,11 @@
       <c r="C11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -796,8 +853,11 @@
       <c r="C12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -807,8 +867,11 @@
       <c r="C13" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -818,8 +881,11 @@
       <c r="C14" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -829,8 +895,11 @@
       <c r="C15" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -840,8 +909,11 @@
       <c r="C16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -851,8 +923,11 @@
       <c r="C17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -862,8 +937,11 @@
       <c r="C18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -873,8 +951,11 @@
       <c r="C19" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -884,8 +965,11 @@
       <c r="C20" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -895,8 +979,11 @@
       <c r="C21" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -906,8 +993,11 @@
       <c r="C22" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -917,8 +1007,11 @@
       <c r="C23" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -928,8 +1021,11 @@
       <c r="C24" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -939,8 +1035,11 @@
       <c r="C25" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -950,8 +1049,11 @@
       <c r="C26" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -961,8 +1063,11 @@
       <c r="C27" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -972,8 +1077,11 @@
       <c r="C28" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -983,8 +1091,11 @@
       <c r="C29" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -994,8 +1105,11 @@
       <c r="C30" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1005,8 +1119,11 @@
       <c r="C31" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1016,8 +1133,11 @@
       <c r="C32" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1027,8 +1147,11 @@
       <c r="C33" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1038,8 +1161,11 @@
       <c r="C34" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1049,8 +1175,11 @@
       <c r="C35" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1060,8 +1189,11 @@
       <c r="C36" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1071,8 +1203,11 @@
       <c r="C37" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1082,8 +1217,11 @@
       <c r="C38" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1093,8 +1231,11 @@
       <c r="C39" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1104,8 +1245,11 @@
       <c r="C40" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1115,8 +1259,11 @@
       <c r="C41" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1126,8 +1273,11 @@
       <c r="C42" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1137,8 +1287,11 @@
       <c r="C43" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1148,8 +1301,11 @@
       <c r="C44" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1159,8 +1315,11 @@
       <c r="C45" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1170,8 +1329,11 @@
       <c r="C46" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1181,8 +1343,11 @@
       <c r="C47" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1192,8 +1357,11 @@
       <c r="C48" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1203,8 +1371,11 @@
       <c r="C49" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1214,8 +1385,11 @@
       <c r="C50" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1225,8 +1399,11 @@
       <c r="C51" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1236,8 +1413,11 @@
       <c r="C52" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1247,8 +1427,11 @@
       <c r="C53" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>60</v>
       </c>
@@ -1258,8 +1441,11 @@
       <c r="C54" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -1269,8 +1455,11 @@
       <c r="C55" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -1280,8 +1469,11 @@
       <c r="C56" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -1291,8 +1483,11 @@
       <c r="C57" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -1302,8 +1497,11 @@
       <c r="C58" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -1313,8 +1511,11 @@
       <c r="C59" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -1324,8 +1525,11 @@
       <c r="C60" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -1335,8 +1539,11 @@
       <c r="C61" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -1346,8 +1553,11 @@
       <c r="C62" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -1357,8 +1567,11 @@
       <c r="C63" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>70</v>
       </c>
@@ -1368,8 +1581,11 @@
       <c r="C64" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>71</v>
       </c>
@@ -1379,8 +1595,11 @@
       <c r="C65" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>72</v>
       </c>
@@ -1390,8 +1609,11 @@
       <c r="C66" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>73</v>
       </c>
@@ -1401,8 +1623,11 @@
       <c r="C67" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>74</v>
       </c>
@@ -1412,8 +1637,11 @@
       <c r="C68" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>75</v>
       </c>
@@ -1423,8 +1651,11 @@
       <c r="C69" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>76</v>
       </c>
@@ -1434,8 +1665,11 @@
       <c r="C70" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>77</v>
       </c>
@@ -1445,8 +1679,11 @@
       <c r="C71" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>78</v>
       </c>
@@ -1456,8 +1693,11 @@
       <c r="C72" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>79</v>
       </c>
@@ -1467,8 +1707,11 @@
       <c r="C73" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>80</v>
       </c>
@@ -1478,8 +1721,11 @@
       <c r="C74" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>81</v>
       </c>
@@ -1489,8 +1735,11 @@
       <c r="C75" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>82</v>
       </c>
@@ -1500,8 +1749,11 @@
       <c r="C76" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -1511,8 +1763,11 @@
       <c r="C77" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>84</v>
       </c>
@@ -1522,8 +1777,11 @@
       <c r="C78" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -1533,8 +1791,11 @@
       <c r="C79" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>86</v>
       </c>
@@ -1543,6 +1804,65 @@
       </c>
       <c r="C80" t="s">
         <v>55</v>
+      </c>
+      <c r="D80" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82" t="s">
+        <v>55</v>
+      </c>
+      <c r="D82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC92EC8A-299F-420B-BDCE-1BBD5061BD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6004D060-B856-4C89-8000-C1FE1BC84C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="98">
   <si>
     <t>Cargo</t>
   </si>
@@ -246,9 +246,6 @@
     <t>Tenico de Ejecucion 14</t>
   </si>
   <si>
-    <t>Tenico de Ejecucion 15</t>
-  </si>
-  <si>
     <t>Auxiliar de Ejecución 1</t>
   </si>
   <si>
@@ -325,6 +322,12 @@
   </si>
   <si>
     <t>Inspector de Seguridad vial 4</t>
+  </si>
+  <si>
+    <t>ZMO FONTIBON III SAS</t>
+  </si>
+  <si>
+    <t>ZMO FONTIBON V SAS</t>
   </si>
 </sst>
 </file>
@@ -682,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -700,7 +703,7 @@
         <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -714,7 +717,7 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,7 +731,7 @@
         <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,7 +745,7 @@
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,7 +759,7 @@
         <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -770,7 +773,7 @@
         <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -784,7 +787,7 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -798,7 +801,7 @@
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -812,7 +815,7 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -826,7 +829,7 @@
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,7 +843,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -854,7 +857,7 @@
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -868,7 +871,7 @@
         <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,7 +885,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,7 +899,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -910,7 +913,7 @@
         <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -924,7 +927,7 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -938,7 +941,7 @@
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -952,7 +955,7 @@
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -966,7 +969,7 @@
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,7 +983,7 @@
         <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -994,7 +997,7 @@
         <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1008,7 +1011,7 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1022,7 +1025,7 @@
         <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1036,7 +1039,7 @@
         <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1050,7 +1053,7 @@
         <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1064,7 +1067,7 @@
         <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1078,7 +1081,7 @@
         <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1092,7 +1095,7 @@
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1106,7 +1109,7 @@
         <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1123,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1134,7 +1137,7 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1148,7 +1151,7 @@
         <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1162,7 +1165,7 @@
         <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1179,7 @@
         <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1190,7 +1193,7 @@
         <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1204,7 +1207,7 @@
         <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1218,7 +1221,7 @@
         <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1232,7 +1235,7 @@
         <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1246,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1260,7 +1263,7 @@
         <v>54</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1274,7 +1277,7 @@
         <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1288,7 +1291,7 @@
         <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1302,7 +1305,7 @@
         <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1316,7 +1319,7 @@
         <v>55</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1330,7 +1333,7 @@
         <v>55</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1344,7 +1347,7 @@
         <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1358,7 +1361,7 @@
         <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1372,7 +1375,7 @@
         <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,13 +1383,13 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C50" t="s">
         <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,13 +1397,13 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
         <v>55</v>
       </c>
       <c r="D51" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1408,13 +1411,13 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
         <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,13 +1425,13 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,13 +1439,13 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
         <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,13 +1453,13 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C55" t="s">
         <v>55</v>
       </c>
       <c r="D55" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,13 +1467,13 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" t="s">
         <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,13 +1481,13 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C57" t="s">
         <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1492,13 +1495,13 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C58" t="s">
         <v>55</v>
       </c>
       <c r="D58" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,13 +1509,13 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" t="s">
         <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,13 +1523,13 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C60" t="s">
         <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1534,13 +1537,13 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" t="s">
         <v>55</v>
       </c>
       <c r="D61" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,13 +1551,13 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C62" t="s">
         <v>55</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1562,13 +1565,13 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
         <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,13 +1579,13 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
         <v>55</v>
       </c>
       <c r="D64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,13 +1593,13 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
         <v>55</v>
       </c>
       <c r="D65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,13 +1607,13 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
         <v>55</v>
       </c>
       <c r="D66" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1618,13 +1621,13 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
         <v>55</v>
       </c>
       <c r="D67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,13 +1635,13 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
         <v>55</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1646,13 +1649,13 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
         <v>55</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,13 +1663,13 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C70" t="s">
         <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,13 +1677,13 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
         <v>55</v>
       </c>
       <c r="D71" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,13 +1691,13 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C72" t="s">
         <v>55</v>
       </c>
       <c r="D72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1702,13 +1705,13 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" t="s">
         <v>55</v>
       </c>
       <c r="D73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,13 +1719,13 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
         <v>55</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,13 +1733,13 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C75" t="s">
         <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1744,13 +1747,13 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
         <v>55</v>
       </c>
       <c r="D76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1758,13 +1761,13 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
         <v>55</v>
       </c>
       <c r="D77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1772,13 +1775,13 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
         <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1786,27 +1789,27 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
         <v>55</v>
       </c>
       <c r="D79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C80" t="s">
         <v>55</v>
       </c>
       <c r="D80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1814,13 +1817,13 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" t="s">
         <v>55</v>
       </c>
       <c r="D81" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1828,13 +1831,13 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C82" t="s">
         <v>55</v>
       </c>
       <c r="D82" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1842,27 +1845,13 @@
         <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83" t="s">
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" t="s">
-        <v>92</v>
-      </c>
-      <c r="C84" t="s">
-        <v>55</v>
-      </c>
-      <c r="D84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6004D060-B856-4C89-8000-C1FE1BC84C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7572D1DB-B3C8-4F85-8080-2CC7933BE44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="59">
   <si>
     <t>Cargo</t>
   </si>
@@ -204,130 +204,13 @@
     <t>Domingo</t>
   </si>
   <si>
-    <t>Tenico de Ejecucion 1</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 2</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 3</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 4</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 5</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 6</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 7</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 8</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 9</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 10</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 11</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 12</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 13</t>
-  </si>
-  <si>
-    <t>Tenico de Ejecucion 14</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 1</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 2</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 3</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 4</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 5</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 6</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 7</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 8</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 9</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 10</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 11</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 12</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 13</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 14</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 15</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución 16</t>
-  </si>
-  <si>
-    <t>Auxiliar de Ejecución de la operación</t>
-  </si>
-  <si>
-    <t>Tecnico Ejecución de la Operación</t>
-  </si>
-  <si>
     <t>Empresa</t>
   </si>
   <si>
     <t>Cablemovil</t>
   </si>
   <si>
-    <t>Greenmovil</t>
-  </si>
-  <si>
-    <t>Inspector de Seguridad vial</t>
-  </si>
-  <si>
-    <t>Inspector de Seguridad vial 1</t>
-  </si>
-  <si>
-    <t>Inspector de Seguridad vial 2</t>
-  </si>
-  <si>
-    <t>Inspector de Seguridad vial 3</t>
-  </si>
-  <si>
-    <t>Inspector de Seguridad vial 4</t>
-  </si>
-  <si>
-    <t>ZMO FONTIBON III SAS</t>
-  </si>
-  <si>
-    <t>ZMO FONTIBON V SAS</t>
+    <t>Viernes</t>
   </si>
 </sst>
 </file>
@@ -685,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:D83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -703,10 +586,10 @@
         <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -717,10 +600,10 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -731,10 +614,10 @@
         <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -745,10 +628,10 @@
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -756,13 +639,13 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -770,13 +653,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -787,10 +670,10 @@
         <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -801,10 +684,10 @@
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -815,10 +698,10 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -829,10 +712,10 @@
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -843,10 +726,10 @@
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -857,10 +740,10 @@
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -871,10 +754,10 @@
         <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -885,10 +768,10 @@
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -899,10 +782,10 @@
         <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -913,10 +796,10 @@
         <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -927,10 +810,10 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -941,10 +824,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -955,10 +838,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -966,13 +849,13 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -980,13 +863,13 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -994,13 +877,13 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1008,13 +891,13 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1022,13 +905,13 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1036,13 +919,13 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1050,13 +933,13 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1064,13 +947,13 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1081,10 +964,10 @@
         <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1095,10 +978,10 @@
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1109,10 +992,10 @@
         <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1123,10 +1006,10 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1137,10 +1020,10 @@
         <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1151,10 +1034,10 @@
         <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1165,10 +1048,10 @@
         <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1179,10 +1062,10 @@
         <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1193,10 +1076,10 @@
         <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1207,10 +1090,10 @@
         <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1221,10 +1104,10 @@
         <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1235,10 +1118,10 @@
         <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1249,10 +1132,10 @@
         <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -1260,13 +1143,13 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -1274,13 +1157,13 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1288,13 +1171,13 @@
         <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1302,13 +1185,13 @@
         <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -1316,13 +1199,13 @@
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -1330,13 +1213,13 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -1347,10 +1230,10 @@
         <v>55</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -1361,10 +1244,10 @@
         <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -1375,483 +1258,7 @@
         <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>55</v>
-      </c>
-      <c r="D52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>55</v>
-      </c>
-      <c r="D53" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" t="s">
-        <v>55</v>
-      </c>
-      <c r="D54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" t="s">
-        <v>87</v>
-      </c>
-      <c r="C56" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" t="s">
-        <v>87</v>
-      </c>
-      <c r="C57" t="s">
-        <v>55</v>
-      </c>
-      <c r="D57" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" t="s">
-        <v>55</v>
-      </c>
-      <c r="D58" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" t="s">
-        <v>55</v>
-      </c>
-      <c r="D59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" t="s">
-        <v>87</v>
-      </c>
-      <c r="C60" t="s">
-        <v>55</v>
-      </c>
-      <c r="D60" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" t="s">
-        <v>87</v>
-      </c>
-      <c r="C61" t="s">
-        <v>55</v>
-      </c>
-      <c r="D61" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" t="s">
-        <v>55</v>
-      </c>
-      <c r="D62" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" t="s">
-        <v>87</v>
-      </c>
-      <c r="C63" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" t="s">
-        <v>86</v>
-      </c>
-      <c r="C64" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s">
-        <v>55</v>
-      </c>
-      <c r="D65" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>55</v>
-      </c>
-      <c r="D67" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" t="s">
-        <v>55</v>
-      </c>
-      <c r="D68" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" t="s">
-        <v>86</v>
-      </c>
-      <c r="C69" t="s">
-        <v>55</v>
-      </c>
-      <c r="D69" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" t="s">
-        <v>86</v>
-      </c>
-      <c r="C70" t="s">
-        <v>55</v>
-      </c>
-      <c r="D70" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" t="s">
-        <v>86</v>
-      </c>
-      <c r="C71" t="s">
-        <v>55</v>
-      </c>
-      <c r="D71" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" t="s">
-        <v>86</v>
-      </c>
-      <c r="C72" t="s">
-        <v>55</v>
-      </c>
-      <c r="D72" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" t="s">
-        <v>86</v>
-      </c>
-      <c r="C73" t="s">
-        <v>55</v>
-      </c>
-      <c r="D73" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" t="s">
-        <v>55</v>
-      </c>
-      <c r="D74" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" t="s">
-        <v>55</v>
-      </c>
-      <c r="D75" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" t="s">
-        <v>86</v>
-      </c>
-      <c r="C76" t="s">
-        <v>55</v>
-      </c>
-      <c r="D76" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" t="s">
-        <v>55</v>
-      </c>
-      <c r="D77" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" t="s">
-        <v>55</v>
-      </c>
-      <c r="D78" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" t="s">
-        <v>86</v>
-      </c>
-      <c r="C79" t="s">
-        <v>55</v>
-      </c>
-      <c r="D79" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>92</v>
-      </c>
-      <c r="B80" t="s">
-        <v>91</v>
-      </c>
-      <c r="C80" t="s">
-        <v>55</v>
-      </c>
-      <c r="D80" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>93</v>
-      </c>
-      <c r="B81" t="s">
-        <v>91</v>
-      </c>
-      <c r="C81" t="s">
-        <v>55</v>
-      </c>
-      <c r="D81" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>94</v>
-      </c>
-      <c r="B82" t="s">
-        <v>91</v>
-      </c>
-      <c r="C82" t="s">
-        <v>55</v>
-      </c>
-      <c r="D82" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>95</v>
-      </c>
-      <c r="B83" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" t="s">
-        <v>55</v>
-      </c>
-      <c r="D83" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7572D1DB-B3C8-4F85-8080-2CC7933BE44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C93B8DA-F7CB-4D50-8E4E-AC9B0C37A224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
@@ -39,159 +39,15 @@
     <t>Cargo</t>
   </si>
   <si>
-    <t>Emp Master 1</t>
-  </si>
-  <si>
     <t>Master</t>
   </si>
   <si>
-    <t>Emp Master 2</t>
-  </si>
-  <si>
-    <t>Emp Master 3</t>
-  </si>
-  <si>
-    <t>Emp Master 4</t>
-  </si>
-  <si>
-    <t>Emp Master 5</t>
-  </si>
-  <si>
-    <t>Emp Master 6</t>
-  </si>
-  <si>
-    <t>Emp Master 7</t>
-  </si>
-  <si>
-    <t>Emp Master 8</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 1</t>
-  </si>
-  <si>
     <t>Tecnico A</t>
   </si>
   <si>
-    <t>Emp Tecnico A 2</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 3</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 4</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 5</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 6</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 7</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 8</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 9</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 10</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 11</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 12</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 13</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 14</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 15</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 16</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 17</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 18</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 19</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 20</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 21</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 22</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 23</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 24</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 25</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 26</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 27</t>
-  </si>
-  <si>
-    <t>Emp Tecnico A 28</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 1</t>
-  </si>
-  <si>
     <t>Tecnico B</t>
   </si>
   <si>
-    <t>Emp Tecnico B 2</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 3</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 4</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 5</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 6</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 7</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 8</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 9</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 10</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 11</t>
-  </si>
-  <si>
-    <t>Emp Tecnico B 12</t>
-  </si>
-  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -211,6 +67,150 @@
   </si>
   <si>
     <t>Viernes</t>
+  </si>
+  <si>
+    <t>BARON HERNANDEZ HAROLD ANTONIO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS CARVAJAL DEYVITH FABIAN</t>
+  </si>
+  <si>
+    <t>DELGADO DELGADO JOHAN DARIO</t>
+  </si>
+  <si>
+    <t>FLOREZ SAUCESO KENIS ALBERTO</t>
+  </si>
+  <si>
+    <t>FONSECA RAY RICARDO</t>
+  </si>
+  <si>
+    <t>GOMEZ BETANCUR JAIDER ANDRES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ MOSQUERA LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>PEPITO PEREZ</t>
+  </si>
+  <si>
+    <t>AROCA TORRES JULIAN EDUARDO</t>
+  </si>
+  <si>
+    <t>BERMUDEZ PARRA JENNIFER XIOMARA</t>
+  </si>
+  <si>
+    <t>BERNAL BAQUERO JAMES RICARDO</t>
+  </si>
+  <si>
+    <t>BURGOS ORTIZ JOSE HORACIO</t>
+  </si>
+  <si>
+    <t>CANTOR PORRAS JUAN FERNEY</t>
+  </si>
+  <si>
+    <t>CAPERA CAPERA JOSE GABRIEL</t>
+  </si>
+  <si>
+    <t>CARDENAS LOTERO RICARDO ANDRÉS</t>
+  </si>
+  <si>
+    <t>CARDONA GARCIA OSCAR JAVIER</t>
+  </si>
+  <si>
+    <t>CARVAJAL GARCÍA HOVER MARCK</t>
+  </si>
+  <si>
+    <t>CEPEDA PIRAQUIVE JUAN DAVID</t>
+  </si>
+  <si>
+    <t>FAJARDO SAENZ OSCAR FERNANDO</t>
+  </si>
+  <si>
+    <t>FLOREZ ESPITIA RONY ALBERTO</t>
+  </si>
+  <si>
+    <t>GARCIA CUERVO EDWIN JAVIER</t>
+  </si>
+  <si>
+    <t>GONZALEZ OCHOA JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>GRANADA PATIÑO CARLOS MARINO</t>
+  </si>
+  <si>
+    <t>GRASS PLATA MIGUEL SNEIDER</t>
+  </si>
+  <si>
+    <t>MANZANO CALVO JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>MENDOZA GOITA MARIANSEL ZENAYDA</t>
+  </si>
+  <si>
+    <t>MURILLO ARAQUE JAIVER GEOVANY</t>
+  </si>
+  <si>
+    <t>NIÑO ARENAS HECTOR GONZALO</t>
+  </si>
+  <si>
+    <t>RAMIREZ CHAVERRA JHON EDISON</t>
+  </si>
+  <si>
+    <t>RAMIREZ VARGAS MARCELA PAOLA</t>
+  </si>
+  <si>
+    <t>SANMARTIN BERRÍO EDUARDO JOSÉ</t>
+  </si>
+  <si>
+    <t>TORO CISNEROS GARY JOSE</t>
+  </si>
+  <si>
+    <t>USECHE CALDERON JADID ESTIVEN</t>
+  </si>
+  <si>
+    <t>VASQUEZ NIETO CAMILO ANDRES</t>
+  </si>
+  <si>
+    <t>JHONY CASTRO</t>
+  </si>
+  <si>
+    <t>BERNAL JUAN DAVID</t>
+  </si>
+  <si>
+    <t>RENDON OSPINA NELSON LEANDRO</t>
+  </si>
+  <si>
+    <t>SARMIENTO URBINA MOISES DANIEL</t>
+  </si>
+  <si>
+    <t>VELASCO VELASCO SEBASTIÁN DAVID</t>
+  </si>
+  <si>
+    <t>XXX1</t>
+  </si>
+  <si>
+    <t>XXX2</t>
+  </si>
+  <si>
+    <t>XXX3</t>
+  </si>
+  <si>
+    <t>XXX4</t>
+  </si>
+  <si>
+    <t>XXX5</t>
+  </si>
+  <si>
+    <t>XXX6</t>
+  </si>
+  <si>
+    <t>XXX7</t>
+  </si>
+  <si>
+    <t>XXX8</t>
+  </si>
+  <si>
+    <t>XXX9</t>
   </si>
 </sst>
 </file>
@@ -571,694 +571,694 @@
   <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" customWidth="1"/>
     <col min="2" max="2" width="25.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C93B8DA-F7CB-4D50-8E4E-AC9B0C37A224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF71B10F-86C0-41DB-82BB-B1156C552AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="-51555" yWindow="195" windowWidth="20325" windowHeight="20370" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="82">
   <si>
     <t>Cargo</t>
   </si>
@@ -51,24 +51,12 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Descanso</t>
-  </si>
-  <si>
-    <t>Sabado</t>
-  </si>
-  <si>
-    <t>Domingo</t>
-  </si>
-  <si>
     <t>Empresa</t>
   </si>
   <si>
     <t>Cablemovil</t>
   </si>
   <si>
-    <t>Viernes</t>
-  </si>
-  <si>
     <t>BARON HERNANDEZ HAROLD ANTONIO</t>
   </si>
   <si>
@@ -211,13 +199,97 @@
   </si>
   <si>
     <t>XXX9</t>
+  </si>
+  <si>
+    <t>Salario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+  </si>
+  <si>
+    <t>AA01</t>
+  </si>
+  <si>
+    <t>AA02</t>
+  </si>
+  <si>
+    <t>AA03</t>
+  </si>
+  <si>
+    <t>AA04</t>
+  </si>
+  <si>
+    <t>AA05</t>
+  </si>
+  <si>
+    <t>AA06</t>
+  </si>
+  <si>
+    <t>AA07</t>
+  </si>
+  <si>
+    <t>AA08</t>
+  </si>
+  <si>
+    <t>AA09</t>
+  </si>
+  <si>
+    <t>AA10</t>
+  </si>
+  <si>
+    <t>AA11</t>
+  </si>
+  <si>
+    <t>AA12</t>
+  </si>
+  <si>
+    <t>AA13</t>
+  </si>
+  <si>
+    <t>AA14</t>
+  </si>
+  <si>
+    <t>AA15</t>
+  </si>
+  <si>
+    <t>AA16</t>
+  </si>
+  <si>
+    <t>AA17</t>
+  </si>
+  <si>
+    <t>AA18</t>
+  </si>
+  <si>
+    <t>AA19</t>
+  </si>
+  <si>
+    <t>AA20</t>
+  </si>
+  <si>
+    <t>AA21</t>
+  </si>
+  <si>
+    <t>AA22</t>
+  </si>
+  <si>
+    <t>AA23</t>
+  </si>
+  <si>
+    <t>AA24</t>
+  </si>
+  <si>
+    <t>AA25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,13 +303,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -249,13 +339,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -568,697 +665,1049 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.81640625" customWidth="1"/>
-    <col min="2" max="2" width="25.7265625" customWidth="1"/>
+    <col min="1" max="1" width="48.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C6" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C7" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C8" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="C9" s="2">
+        <v>4028000</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="B27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="B29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="B31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="B33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="B34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="B35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B32" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="B36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B33" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="B37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B34" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="B38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B35" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="B39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="B40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B37" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="B41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="C42" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C39" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="C43" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B44" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C40" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="C44" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C41" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="C45" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="C46" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C43" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="C47" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="C48" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C45" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="C49" s="2">
+        <v>2544000</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="B50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B49" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" t="s">
-        <v>9</v>
+      <c r="B51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF71B10F-86C0-41DB-82BB-B1156C552AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196BE000-849F-42CD-B73D-E891DDE1CE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51555" yWindow="195" windowWidth="20325" windowHeight="20370" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -345,7 +345,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
